--- a/quizzes/023_first_person_shooter_skills_quiz--quizzes.xlsx
+++ b/quizzes/023_first_person_shooter_skills_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -779,53 +779,53 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ammunition</t>
+          <t>awareness</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ammunition</t>
+          <t>Awareness</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>player_knowledge_choices</t>
+          <t>situational_awareness_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>agility</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>player_knowledge_choices</t>
+          <t>situational_awareness_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>awareness</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>player_knowledge_choices</t>
+          <t>game_theory_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -842,187 +842,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>player_knowledge_choices</t>
+          <t>game_theory_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ammunition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ammunition</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>player_knowledge_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ammunition</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ammunition</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>situational_awareness_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>situational_awareness_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>game_theory_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ammunition</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ammunition</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>game_theory_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ammunition</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ammunition</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>game_theory_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ammunition</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ammunition</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>game_theory_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ammunition</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ammunition</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>game_theory_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ammunition</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ammunition</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>game_theory_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ammunition</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ammunition</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>game_theory_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ammunition</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ammunition</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
